--- a/Result/profitability/3444.xlsx
+++ b/Result/profitability/3444.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.57375</v>
+        <v>0.63375</v>
       </c>
       <c r="N2" t="n">
-        <v>22.225</v>
+        <v>21.43375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6525</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>21.9375</v>
+        <v>21.61375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.87</v>
       </c>
       <c r="M4" t="n">
-        <v>0.66125</v>
+        <v>0.6425000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>21.27</v>
+        <v>20.71375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5175</v>
+        <v>0.54625</v>
       </c>
       <c r="N5" t="n">
-        <v>19.735</v>
+        <v>19.4425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4950000000000001</v>
+        <v>0.52125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.14375</v>
+        <v>19.0825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.525</v>
+        <v>0.54125</v>
       </c>
       <c r="N7" t="n">
-        <v>19.2175</v>
+        <v>19.4125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.53125</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>19.1675</v>
+        <v>19.155</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3444</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>337</v>
+      </c>
+      <c r="D75" t="n">
+        <v>271</v>
+      </c>
+      <c r="E75" t="n">
+        <v>66</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>29</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.5025</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1000000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005060728744939347</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1063636363636363</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
